--- a/dados_fontes/GNS_Analise.xlsx
+++ b/dados_fontes/GNS_Analise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/jonathan_goncalvessilva_claro_com_br/Documents/Jonathan/Spam/Canal360_Prototipo_React_V5_Gerencial/canal360-react/dados_fontes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="599" documentId="8_{DCD825F7-B954-4D03-BCC1-91C11040243C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07BF0367-5837-4751-A991-9A08E66680CB}"/>
+  <xr:revisionPtr revIDLastSave="600" documentId="8_{DCD825F7-B954-4D03-BCC1-91C11040243C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3BCE3A6-F193-4266-AAC1-493CC7960A90}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="752" activeTab="1" xr2:uid="{4882413C-ABE9-466C-BC2C-9360E9CE520F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="752" activeTab="1" xr2:uid="{4882413C-ABE9-466C-BC2C-9360E9CE520F}"/>
   </bookViews>
   <sheets>
     <sheet name="PARAMETRO" sheetId="17" r:id="rId1"/>
@@ -3403,20 +3403,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5C5F76-B33A-48A8-9C59-66F30A389D2C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="13.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3486,45 +3486,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0BB3401-F945-46E8-B4F3-7B13F6D043E4}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:AR205"/>
-  <sheetFormatPr defaultColWidth="17" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="17" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.08984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="41.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="103.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="103.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.81640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.54296875" style="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.6328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="25.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="24" max="35" width="11.08984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="36" max="39" width="13.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="4.6328125" style="1" customWidth="1"/>
-    <col min="43" max="43" width="4.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.6328125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.5546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="24" max="35" width="11.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="36" max="39" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="4.6640625" style="1" customWidth="1"/>
+    <col min="43" max="43" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.6640625" style="1" customWidth="1"/>
     <col min="45" max="16384" width="17" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="10" customFormat="1" ht="142">
+    <row r="1" spans="1:44" s="10" customFormat="1" ht="141">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="14" hidden="1">
+    <row r="2" spans="1:44" ht="13.8">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="14" hidden="1">
+    <row r="3" spans="1:44" ht="13.8">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="14">
+    <row r="4" spans="1:44" ht="13.8">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="14">
+    <row r="5" spans="1:44" ht="13.8">
       <c r="A5" s="5" t="s">
         <v>152</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="14">
+    <row r="6" spans="1:44" ht="13.8">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="14" hidden="1">
+    <row r="7" spans="1:44" ht="13.8">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="14" hidden="1">
+    <row r="8" spans="1:44" ht="13.8">
       <c r="A8" s="5" t="s">
         <v>153</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="14">
+    <row r="9" spans="1:44" ht="13.8">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="14" hidden="1">
+    <row r="10" spans="1:44" ht="13.8">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="11" spans="1:44" ht="14" hidden="1">
+    <row r="11" spans="1:44" ht="13.8">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="14">
+    <row r="12" spans="1:44" ht="13.8">
       <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="14" hidden="1">
+    <row r="13" spans="1:44" ht="13.8">
       <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="14" spans="1:44" ht="14">
+    <row r="14" spans="1:44" ht="13.8">
       <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="14" hidden="1">
+    <row r="15" spans="1:44" ht="13.8">
       <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="14">
+    <row r="16" spans="1:44" ht="13.8">
       <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="17" spans="1:44" ht="14">
+    <row r="17" spans="1:44" ht="13.8">
       <c r="A17" s="5" t="s">
         <v>14</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="18" spans="1:44" ht="14" hidden="1">
+    <row r="18" spans="1:44" ht="13.8">
       <c r="A18" s="5" t="s">
         <v>15</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="14">
+    <row r="19" spans="1:44" ht="13.8">
       <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="20" spans="1:44" ht="14" hidden="1">
+    <row r="20" spans="1:44" ht="13.8">
       <c r="A20" s="5" t="s">
         <v>17</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="14" hidden="1">
+    <row r="21" spans="1:44" ht="13.8">
       <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="22" spans="1:44" ht="14" hidden="1">
+    <row r="22" spans="1:44" ht="13.8">
       <c r="A22" s="5" t="s">
         <v>19</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="23" spans="1:44" ht="14" hidden="1">
+    <row r="23" spans="1:44" ht="13.8">
       <c r="A23" s="5" t="s">
         <v>20</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="24" spans="1:44" ht="14">
+    <row r="24" spans="1:44" ht="13.8">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="14" hidden="1">
+    <row r="25" spans="1:44" ht="13.8">
       <c r="A25" s="5" t="s">
         <v>154</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="26" spans="1:44" ht="14">
+    <row r="26" spans="1:44" ht="13.8">
       <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="27" spans="1:44" ht="14" hidden="1">
+    <row r="27" spans="1:44" ht="13.8">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="28" spans="1:44" ht="14" hidden="1">
+    <row r="28" spans="1:44" ht="13.8">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="29" spans="1:44" ht="14" hidden="1">
+    <row r="29" spans="1:44" ht="13.8">
       <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="30" spans="1:44" ht="14">
+    <row r="30" spans="1:44" ht="13.8">
       <c r="A30" s="5" t="s">
         <v>339</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="31" spans="1:44" ht="14" hidden="1">
+    <row r="31" spans="1:44" ht="13.8">
       <c r="A31" s="5" t="s">
         <v>26</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="32" spans="1:44" ht="14">
+    <row r="32" spans="1:44" ht="13.8">
       <c r="A32" s="5" t="s">
         <v>340</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="33" spans="1:44" ht="14">
+    <row r="33" spans="1:44" ht="13.8">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="34" spans="1:44" ht="14" hidden="1">
+    <row r="34" spans="1:44" ht="13.8">
       <c r="A34" s="5" t="s">
         <v>155</v>
       </c>
@@ -8080,7 +8080,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="35" spans="1:44" ht="14" hidden="1">
+    <row r="35" spans="1:44" ht="13.8">
       <c r="A35" s="5" t="s">
         <v>28</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="36" spans="1:44" ht="14" hidden="1">
+    <row r="36" spans="1:44" ht="13.8">
       <c r="A36" s="5" t="s">
         <v>29</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="37" spans="1:44" ht="14" hidden="1">
+    <row r="37" spans="1:44" ht="13.8">
       <c r="A37" s="5" t="s">
         <v>144</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="38" spans="1:44" ht="14" hidden="1">
+    <row r="38" spans="1:44" ht="13.8">
       <c r="A38" s="5" t="s">
         <v>30</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="39" spans="1:44" ht="14" hidden="1">
+    <row r="39" spans="1:44" ht="13.8">
       <c r="A39" s="5" t="s">
         <v>31</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="40" spans="1:44" ht="14" hidden="1">
+    <row r="40" spans="1:44" ht="13.8">
       <c r="A40" s="5" t="s">
         <v>32</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="41" spans="1:44" ht="14">
+    <row r="41" spans="1:44" ht="13.8">
       <c r="A41" s="5" t="s">
         <v>156</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="42" spans="1:44" ht="14" hidden="1">
+    <row r="42" spans="1:44" ht="13.8">
       <c r="A42" s="5" t="s">
         <v>33</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="43" spans="1:44" ht="14">
+    <row r="43" spans="1:44" ht="13.8">
       <c r="A43" s="5" t="s">
         <v>34</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="44" spans="1:44" ht="14" hidden="1">
+    <row r="44" spans="1:44" ht="13.8">
       <c r="A44" s="5" t="s">
         <v>341</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="45" spans="1:44" ht="14" hidden="1">
+    <row r="45" spans="1:44" ht="13.8">
       <c r="A45" s="5" t="s">
         <v>35</v>
       </c>
@@ -9554,7 +9554,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="46" spans="1:44" ht="14">
+    <row r="46" spans="1:44" ht="13.8">
       <c r="A46" s="5" t="s">
         <v>36</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="47" spans="1:44" ht="14" hidden="1">
+    <row r="47" spans="1:44" ht="13.8">
       <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="48" spans="1:44" ht="14" hidden="1">
+    <row r="48" spans="1:44" ht="13.8">
       <c r="A48" s="5" t="s">
         <v>157</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="49" spans="1:44" ht="14">
+    <row r="49" spans="1:44" ht="13.8">
       <c r="A49" s="5" t="s">
         <v>38</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="50" spans="1:44" ht="14" hidden="1">
+    <row r="50" spans="1:44" ht="13.8">
       <c r="A50" s="5" t="s">
         <v>39</v>
       </c>
@@ -10224,7 +10224,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="51" spans="1:44" ht="14" hidden="1">
+    <row r="51" spans="1:44" ht="13.8">
       <c r="A51" s="5" t="s">
         <v>158</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="52" spans="1:44" ht="14" hidden="1">
+    <row r="52" spans="1:44" ht="13.8">
       <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="53" spans="1:44" ht="14">
+    <row r="53" spans="1:44" ht="13.8">
       <c r="A53" s="5" t="s">
         <v>159</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="54" spans="1:44" ht="14">
+    <row r="54" spans="1:44" ht="13.8">
       <c r="A54" s="5" t="s">
         <v>148</v>
       </c>
@@ -10760,7 +10760,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="55" spans="1:44" ht="14">
+    <row r="55" spans="1:44" ht="13.8">
       <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="56" spans="1:44" ht="14">
+    <row r="56" spans="1:44" ht="13.8">
       <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="57" spans="1:44" ht="14" hidden="1">
+    <row r="57" spans="1:44" ht="13.8">
       <c r="A57" s="5" t="s">
         <v>43</v>
       </c>
@@ -11162,7 +11162,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="58" spans="1:44" ht="14" hidden="1">
+    <row r="58" spans="1:44" ht="13.8">
       <c r="A58" s="5" t="s">
         <v>44</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="59" spans="1:44" ht="14">
+    <row r="59" spans="1:44" ht="13.8">
       <c r="A59" s="5" t="s">
         <v>149</v>
       </c>
@@ -11430,7 +11430,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="60" spans="1:44" ht="14">
+    <row r="60" spans="1:44" ht="13.8">
       <c r="A60" s="5" t="s">
         <v>45</v>
       </c>
@@ -11564,7 +11564,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="61" spans="1:44" ht="14" hidden="1">
+    <row r="61" spans="1:44" ht="13.8">
       <c r="A61" s="5" t="s">
         <v>46</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="62" spans="1:44" ht="14" hidden="1">
+    <row r="62" spans="1:44" ht="13.8">
       <c r="A62" s="5" t="s">
         <v>47</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="63" spans="1:44" ht="14" hidden="1">
+    <row r="63" spans="1:44" ht="13.8">
       <c r="A63" s="5" t="s">
         <v>48</v>
       </c>
@@ -11966,7 +11966,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="64" spans="1:44" ht="14" hidden="1">
+    <row r="64" spans="1:44" ht="13.8">
       <c r="A64" s="5" t="s">
         <v>343</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="65" spans="1:44" ht="14">
+    <row r="65" spans="1:44" ht="13.8">
       <c r="A65" s="5" t="s">
         <v>49</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="66" spans="1:44" ht="14">
+    <row r="66" spans="1:44" ht="13.8">
       <c r="A66" s="5" t="s">
         <v>50</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="67" spans="1:44" ht="14" hidden="1">
+    <row r="67" spans="1:44" ht="13.8">
       <c r="A67" s="5" t="s">
         <v>51</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="68" spans="1:44" ht="14" hidden="1">
+    <row r="68" spans="1:44" ht="13.8">
       <c r="A68" s="5" t="s">
         <v>52</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="69" spans="1:44" ht="14" hidden="1">
+    <row r="69" spans="1:44" ht="13.8">
       <c r="A69" s="5" t="s">
         <v>53</v>
       </c>
@@ -12770,7 +12770,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="70" spans="1:44" ht="14">
+    <row r="70" spans="1:44" ht="13.8">
       <c r="A70" s="5" t="s">
         <v>160</v>
       </c>
@@ -12904,7 +12904,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="71" spans="1:44" ht="14" hidden="1">
+    <row r="71" spans="1:44" ht="13.8">
       <c r="A71" s="5" t="s">
         <v>54</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="72" spans="1:44" ht="14" hidden="1">
+    <row r="72" spans="1:44" ht="13.8">
       <c r="A72" s="5" t="s">
         <v>55</v>
       </c>
@@ -13172,7 +13172,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="73" spans="1:44" ht="14" hidden="1">
+    <row r="73" spans="1:44" ht="13.8">
       <c r="A73" s="5" t="s">
         <v>56</v>
       </c>
@@ -13306,7 +13306,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="74" spans="1:44" ht="14" hidden="1">
+    <row r="74" spans="1:44" ht="13.8">
       <c r="A74" s="5" t="s">
         <v>57</v>
       </c>
@@ -13440,7 +13440,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="75" spans="1:44" ht="14">
+    <row r="75" spans="1:44" ht="13.8">
       <c r="A75" s="5" t="s">
         <v>58</v>
       </c>
@@ -13574,7 +13574,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="76" spans="1:44" ht="14" hidden="1">
+    <row r="76" spans="1:44" ht="13.8">
       <c r="A76" s="5" t="s">
         <v>59</v>
       </c>
@@ -13708,7 +13708,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="77" spans="1:44" ht="14" hidden="1">
+    <row r="77" spans="1:44" ht="13.8">
       <c r="A77" s="5" t="s">
         <v>60</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="78" spans="1:44" ht="14">
+    <row r="78" spans="1:44" ht="13.8">
       <c r="A78" s="5" t="s">
         <v>61</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="79" spans="1:44" ht="14">
+    <row r="79" spans="1:44" ht="13.8">
       <c r="A79" s="5" t="s">
         <v>345</v>
       </c>
@@ -14110,7 +14110,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="80" spans="1:44" ht="14" hidden="1">
+    <row r="80" spans="1:44" ht="13.8">
       <c r="A80" s="5" t="s">
         <v>161</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="81" spans="1:44" ht="14">
+    <row r="81" spans="1:44" ht="13.8">
       <c r="A81" s="5" t="s">
         <v>62</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="82" spans="1:44" ht="14">
+    <row r="82" spans="1:44" ht="13.8">
       <c r="A82" s="5" t="s">
         <v>63</v>
       </c>
@@ -14512,7 +14512,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="83" spans="1:44" ht="14">
+    <row r="83" spans="1:44" ht="13.8">
       <c r="A83" s="5" t="s">
         <v>64</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="84" spans="1:44" ht="14" hidden="1">
+    <row r="84" spans="1:44" ht="13.8">
       <c r="A84" s="5" t="s">
         <v>65</v>
       </c>
@@ -14780,7 +14780,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="85" spans="1:44" ht="14">
+    <row r="85" spans="1:44" ht="13.8">
       <c r="A85" s="5" t="s">
         <v>66</v>
       </c>
@@ -14914,7 +14914,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="86" spans="1:44" ht="14" hidden="1">
+    <row r="86" spans="1:44" ht="13.8">
       <c r="A86" s="5" t="s">
         <v>162</v>
       </c>
@@ -15048,7 +15048,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="87" spans="1:44" ht="14">
+    <row r="87" spans="1:44" ht="13.8">
       <c r="A87" s="5" t="s">
         <v>67</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="88" spans="1:44" ht="14" hidden="1">
+    <row r="88" spans="1:44" ht="13.8">
       <c r="A88" s="5" t="s">
         <v>68</v>
       </c>
@@ -15316,7 +15316,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="89" spans="1:44" ht="14" hidden="1">
+    <row r="89" spans="1:44" ht="13.8">
       <c r="A89" s="5" t="s">
         <v>69</v>
       </c>
@@ -15450,7 +15450,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="90" spans="1:44" ht="14">
+    <row r="90" spans="1:44" ht="13.8">
       <c r="A90" s="5" t="s">
         <v>150</v>
       </c>
@@ -15584,7 +15584,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="91" spans="1:44" ht="14" hidden="1">
+    <row r="91" spans="1:44" ht="13.8">
       <c r="A91" s="5" t="s">
         <v>70</v>
       </c>
@@ -15718,7 +15718,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="92" spans="1:44" ht="14" hidden="1">
+    <row r="92" spans="1:44" ht="13.8">
       <c r="A92" s="5" t="s">
         <v>71</v>
       </c>
@@ -15852,7 +15852,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="93" spans="1:44" ht="14" hidden="1">
+    <row r="93" spans="1:44" ht="13.8">
       <c r="A93" s="5" t="s">
         <v>72</v>
       </c>
@@ -15986,7 +15986,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="94" spans="1:44" ht="14" hidden="1">
+    <row r="94" spans="1:44" ht="13.8">
       <c r="A94" s="5" t="s">
         <v>73</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="95" spans="1:44" ht="14">
+    <row r="95" spans="1:44" ht="13.8">
       <c r="A95" s="5" t="s">
         <v>74</v>
       </c>
@@ -16254,7 +16254,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="96" spans="1:44" ht="14">
+    <row r="96" spans="1:44" ht="13.8">
       <c r="A96" s="5" t="s">
         <v>75</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="97" spans="1:44" ht="14" hidden="1">
+    <row r="97" spans="1:44" ht="13.8">
       <c r="A97" s="5" t="s">
         <v>163</v>
       </c>
@@ -16522,7 +16522,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="98" spans="1:44" ht="14" hidden="1">
+    <row r="98" spans="1:44" ht="13.8">
       <c r="A98" s="5" t="s">
         <v>76</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="99" spans="1:44" ht="14" hidden="1">
+    <row r="99" spans="1:44" ht="13.8">
       <c r="A99" s="5" t="s">
         <v>77</v>
       </c>
@@ -16790,7 +16790,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="100" spans="1:44" ht="14" hidden="1">
+    <row r="100" spans="1:44" ht="13.8">
       <c r="A100" s="5" t="s">
         <v>78</v>
       </c>
@@ -16924,7 +16924,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="101" spans="1:44" ht="14">
+    <row r="101" spans="1:44" ht="13.8">
       <c r="A101" s="5" t="s">
         <v>79</v>
       </c>
@@ -17058,7 +17058,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="102" spans="1:44" ht="14" hidden="1">
+    <row r="102" spans="1:44" ht="13.8">
       <c r="A102" s="5" t="s">
         <v>146</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="103" spans="1:44" ht="14">
+    <row r="103" spans="1:44" ht="13.8">
       <c r="A103" s="5" t="s">
         <v>173</v>
       </c>
@@ -17326,7 +17326,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="104" spans="1:44" ht="14">
+    <row r="104" spans="1:44" ht="13.8">
       <c r="A104" s="5" t="s">
         <v>80</v>
       </c>
@@ -17460,7 +17460,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="105" spans="1:44" ht="14" hidden="1">
+    <row r="105" spans="1:44" ht="13.8">
       <c r="A105" s="5" t="s">
         <v>81</v>
       </c>
@@ -17594,7 +17594,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="106" spans="1:44" ht="14" hidden="1">
+    <row r="106" spans="1:44" ht="13.8">
       <c r="A106" s="5" t="s">
         <v>164</v>
       </c>
@@ -17728,7 +17728,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="107" spans="1:44" ht="14" hidden="1">
+    <row r="107" spans="1:44" ht="13.8">
       <c r="A107" s="5" t="s">
         <v>82</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="108" spans="1:44" ht="14" hidden="1">
+    <row r="108" spans="1:44" ht="13.8">
       <c r="A108" s="5" t="s">
         <v>83</v>
       </c>
@@ -17996,7 +17996,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="109" spans="1:44" ht="14">
+    <row r="109" spans="1:44" ht="13.8">
       <c r="A109" s="5" t="s">
         <v>84</v>
       </c>
@@ -18130,7 +18130,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="110" spans="1:44" ht="14" hidden="1">
+    <row r="110" spans="1:44" ht="13.8">
       <c r="A110" s="5" t="s">
         <v>85</v>
       </c>
@@ -18264,7 +18264,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="111" spans="1:44" ht="14" hidden="1">
+    <row r="111" spans="1:44" ht="13.8">
       <c r="A111" s="5" t="s">
         <v>86</v>
       </c>
@@ -18398,7 +18398,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="112" spans="1:44" ht="14">
+    <row r="112" spans="1:44" ht="13.8">
       <c r="A112" s="5" t="s">
         <v>87</v>
       </c>
@@ -18532,7 +18532,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="113" spans="1:44" ht="14" hidden="1">
+    <row r="113" spans="1:44" ht="13.8">
       <c r="A113" s="5" t="s">
         <v>165</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="114" spans="1:44" ht="14" hidden="1">
+    <row r="114" spans="1:44" ht="13.8">
       <c r="A114" s="5" t="s">
         <v>88</v>
       </c>
@@ -18800,7 +18800,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="115" spans="1:44" ht="14">
+    <row r="115" spans="1:44" ht="13.8">
       <c r="A115" s="5" t="s">
         <v>89</v>
       </c>
@@ -18934,7 +18934,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="116" spans="1:44" ht="14" hidden="1">
+    <row r="116" spans="1:44" ht="13.8">
       <c r="A116" s="5" t="s">
         <v>90</v>
       </c>
@@ -19068,7 +19068,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="117" spans="1:44" ht="14" hidden="1">
+    <row r="117" spans="1:44" ht="13.8">
       <c r="A117" s="5" t="s">
         <v>147</v>
       </c>
@@ -19202,7 +19202,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="118" spans="1:44" ht="14" hidden="1">
+    <row r="118" spans="1:44" ht="13.8">
       <c r="A118" s="5" t="s">
         <v>91</v>
       </c>
@@ -19336,7 +19336,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="119" spans="1:44" ht="14">
+    <row r="119" spans="1:44" ht="13.8">
       <c r="A119" s="5" t="s">
         <v>166</v>
       </c>
@@ -19470,7 +19470,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="120" spans="1:44" ht="14" hidden="1">
+    <row r="120" spans="1:44" ht="13.8">
       <c r="A120" s="5" t="s">
         <v>92</v>
       </c>
@@ -19604,7 +19604,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="121" spans="1:44" ht="14" hidden="1">
+    <row r="121" spans="1:44" ht="13.8">
       <c r="A121" s="5" t="s">
         <v>167</v>
       </c>
@@ -19738,7 +19738,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="122" spans="1:44" ht="14">
+    <row r="122" spans="1:44" ht="13.8">
       <c r="A122" s="5" t="s">
         <v>93</v>
       </c>
@@ -19872,7 +19872,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="123" spans="1:44" ht="14">
+    <row r="123" spans="1:44" ht="13.8">
       <c r="A123" s="5" t="s">
         <v>94</v>
       </c>
@@ -20006,7 +20006,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="124" spans="1:44" ht="14" hidden="1">
+    <row r="124" spans="1:44" ht="13.8">
       <c r="A124" s="5" t="s">
         <v>95</v>
       </c>
@@ -20140,7 +20140,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="125" spans="1:44" ht="14" hidden="1">
+    <row r="125" spans="1:44" ht="13.8">
       <c r="A125" s="5" t="s">
         <v>168</v>
       </c>
@@ -20274,7 +20274,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="126" spans="1:44" ht="14" hidden="1">
+    <row r="126" spans="1:44" ht="13.8">
       <c r="A126" s="5" t="s">
         <v>96</v>
       </c>
@@ -20408,7 +20408,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="127" spans="1:44" ht="14" hidden="1">
+    <row r="127" spans="1:44" ht="13.8">
       <c r="A127" s="5" t="s">
         <v>97</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="128" spans="1:44" ht="14" hidden="1">
+    <row r="128" spans="1:44" ht="13.8">
       <c r="A128" s="5" t="s">
         <v>98</v>
       </c>
@@ -20676,7 +20676,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="129" spans="1:44" ht="14" hidden="1">
+    <row r="129" spans="1:44" ht="13.8">
       <c r="A129" s="5" t="s">
         <v>99</v>
       </c>
@@ -20810,7 +20810,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="130" spans="1:44" ht="14" hidden="1">
+    <row r="130" spans="1:44" ht="13.8">
       <c r="A130" s="5" t="s">
         <v>100</v>
       </c>
@@ -20944,7 +20944,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="131" spans="1:44" ht="14" hidden="1">
+    <row r="131" spans="1:44" ht="13.8">
       <c r="A131" s="5" t="s">
         <v>101</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="132" spans="1:44" ht="14" hidden="1">
+    <row r="132" spans="1:44" ht="13.8">
       <c r="A132" s="5" t="s">
         <v>102</v>
       </c>
@@ -21212,7 +21212,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="133" spans="1:44" ht="14" hidden="1">
+    <row r="133" spans="1:44" ht="13.8">
       <c r="A133" s="5" t="s">
         <v>103</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="134" spans="1:44" ht="14" hidden="1">
+    <row r="134" spans="1:44" ht="13.8">
       <c r="A134" s="5" t="s">
         <v>104</v>
       </c>
@@ -21480,7 +21480,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="135" spans="1:44" ht="14" hidden="1">
+    <row r="135" spans="1:44" ht="13.8">
       <c r="A135" s="5" t="s">
         <v>105</v>
       </c>
@@ -21614,7 +21614,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="136" spans="1:44" ht="14" hidden="1">
+    <row r="136" spans="1:44" ht="13.8">
       <c r="A136" s="5" t="s">
         <v>106</v>
       </c>
@@ -21748,7 +21748,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="137" spans="1:44" ht="14" hidden="1">
+    <row r="137" spans="1:44" ht="13.8">
       <c r="A137" s="5" t="s">
         <v>107</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="138" spans="1:44" ht="14" hidden="1">
+    <row r="138" spans="1:44" ht="13.8">
       <c r="A138" s="5" t="s">
         <v>108</v>
       </c>
@@ -22016,7 +22016,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="139" spans="1:44" ht="14">
+    <row r="139" spans="1:44" ht="13.8">
       <c r="A139" s="5" t="s">
         <v>347</v>
       </c>
@@ -22150,7 +22150,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="140" spans="1:44" ht="14" hidden="1">
+    <row r="140" spans="1:44" ht="13.8">
       <c r="A140" s="5" t="s">
         <v>109</v>
       </c>
@@ -22284,7 +22284,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="141" spans="1:44" ht="14" hidden="1">
+    <row r="141" spans="1:44" ht="13.8">
       <c r="A141" s="5" t="s">
         <v>110</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="142" spans="1:44" ht="14" hidden="1">
+    <row r="142" spans="1:44" ht="13.8">
       <c r="A142" s="5" t="s">
         <v>111</v>
       </c>
@@ -22552,7 +22552,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="143" spans="1:44" ht="14" hidden="1">
+    <row r="143" spans="1:44" ht="13.8">
       <c r="A143" s="5" t="s">
         <v>112</v>
       </c>
@@ -22686,7 +22686,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="144" spans="1:44" ht="14" hidden="1">
+    <row r="144" spans="1:44" ht="13.8">
       <c r="A144" s="5" t="s">
         <v>113</v>
       </c>
@@ -22820,7 +22820,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="145" spans="1:44" ht="14" hidden="1">
+    <row r="145" spans="1:44" ht="13.8">
       <c r="A145" s="5" t="s">
         <v>114</v>
       </c>
@@ -22954,7 +22954,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="146" spans="1:44" ht="14" hidden="1">
+    <row r="146" spans="1:44" ht="13.8">
       <c r="A146" s="5" t="s">
         <v>115</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="147" spans="1:44" ht="14" hidden="1">
+    <row r="147" spans="1:44" ht="13.8">
       <c r="A147" s="5" t="s">
         <v>116</v>
       </c>
@@ -23222,7 +23222,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="148" spans="1:44" ht="14" hidden="1">
+    <row r="148" spans="1:44" ht="13.8">
       <c r="A148" s="5" t="s">
         <v>117</v>
       </c>
@@ -23356,7 +23356,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="149" spans="1:44" ht="14" hidden="1">
+    <row r="149" spans="1:44" ht="13.8">
       <c r="A149" s="5" t="s">
         <v>118</v>
       </c>
@@ -23490,7 +23490,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="150" spans="1:44" ht="14" hidden="1">
+    <row r="150" spans="1:44" ht="13.8">
       <c r="A150" s="5" t="s">
         <v>119</v>
       </c>
@@ -23624,7 +23624,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="151" spans="1:44" ht="14" hidden="1">
+    <row r="151" spans="1:44" ht="13.8">
       <c r="A151" s="5" t="s">
         <v>120</v>
       </c>
@@ -23758,7 +23758,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="152" spans="1:44" ht="14" hidden="1">
+    <row r="152" spans="1:44" ht="13.8">
       <c r="A152" s="5" t="s">
         <v>121</v>
       </c>
@@ -23892,7 +23892,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="153" spans="1:44" ht="14" hidden="1">
+    <row r="153" spans="1:44" ht="13.8">
       <c r="A153" s="5" t="s">
         <v>122</v>
       </c>
@@ -24026,7 +24026,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="154" spans="1:44" ht="14">
+    <row r="154" spans="1:44" ht="13.8">
       <c r="A154" s="5" t="s">
         <v>123</v>
       </c>
@@ -24160,7 +24160,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="155" spans="1:44" ht="14">
+    <row r="155" spans="1:44" ht="13.8">
       <c r="A155" s="5" t="s">
         <v>124</v>
       </c>
@@ -24294,7 +24294,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="156" spans="1:44" ht="14" hidden="1">
+    <row r="156" spans="1:44" ht="13.8">
       <c r="A156" s="5" t="s">
         <v>125</v>
       </c>
@@ -24428,7 +24428,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="157" spans="1:44" ht="14" hidden="1">
+    <row r="157" spans="1:44" ht="13.8">
       <c r="A157" s="5" t="s">
         <v>143</v>
       </c>
@@ -24562,7 +24562,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="158" spans="1:44" ht="14" hidden="1">
+    <row r="158" spans="1:44" ht="13.8">
       <c r="A158" s="5" t="s">
         <v>126</v>
       </c>
@@ -24696,7 +24696,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="159" spans="1:44" ht="14" hidden="1">
+    <row r="159" spans="1:44" ht="13.8">
       <c r="A159" s="5" t="s">
         <v>127</v>
       </c>
@@ -24830,7 +24830,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="160" spans="1:44" ht="14" hidden="1">
+    <row r="160" spans="1:44" ht="13.8">
       <c r="A160" s="5" t="s">
         <v>128</v>
       </c>
@@ -24964,7 +24964,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="161" spans="1:44" ht="14">
+    <row r="161" spans="1:44" ht="13.8">
       <c r="A161" s="5" t="s">
         <v>129</v>
       </c>
@@ -25098,7 +25098,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="162" spans="1:44" ht="14" hidden="1">
+    <row r="162" spans="1:44" ht="13.8">
       <c r="A162" s="5" t="s">
         <v>130</v>
       </c>
@@ -25232,7 +25232,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="163" spans="1:44" ht="14" hidden="1">
+    <row r="163" spans="1:44" ht="13.8">
       <c r="A163" s="5" t="s">
         <v>131</v>
       </c>
@@ -25366,7 +25366,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="164" spans="1:44" ht="14" hidden="1">
+    <row r="164" spans="1:44" ht="13.8">
       <c r="A164" s="5" t="s">
         <v>132</v>
       </c>
@@ -25500,7 +25500,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="165" spans="1:44" ht="14" hidden="1">
+    <row r="165" spans="1:44" ht="13.8">
       <c r="A165" s="5" t="s">
         <v>133</v>
       </c>
@@ -25634,7 +25634,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="166" spans="1:44" ht="14" hidden="1">
+    <row r="166" spans="1:44" ht="13.8">
       <c r="A166" s="5" t="s">
         <v>134</v>
       </c>
@@ -25768,7 +25768,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="167" spans="1:44" ht="14" hidden="1">
+    <row r="167" spans="1:44" ht="13.8">
       <c r="A167" s="5" t="s">
         <v>135</v>
       </c>
@@ -25902,7 +25902,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="168" spans="1:44" ht="14">
+    <row r="168" spans="1:44" ht="13.8">
       <c r="A168" s="5" t="s">
         <v>136</v>
       </c>
@@ -26036,7 +26036,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="169" spans="1:44" ht="14">
+    <row r="169" spans="1:44" ht="13.8">
       <c r="A169" s="5" t="s">
         <v>151</v>
       </c>
@@ -26170,7 +26170,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="170" spans="1:44" ht="14" hidden="1">
+    <row r="170" spans="1:44" ht="13.8">
       <c r="A170" s="5" t="s">
         <v>169</v>
       </c>
@@ -26304,7 +26304,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="171" spans="1:44" ht="14" hidden="1">
+    <row r="171" spans="1:44" ht="13.8">
       <c r="A171" s="5" t="s">
         <v>137</v>
       </c>
@@ -26438,7 +26438,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="172" spans="1:44" ht="14">
+    <row r="172" spans="1:44" ht="13.8">
       <c r="A172" s="5" t="s">
         <v>348</v>
       </c>
@@ -26572,7 +26572,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="173" spans="1:44" ht="14" hidden="1">
+    <row r="173" spans="1:44" ht="13.8">
       <c r="A173" s="5" t="s">
         <v>170</v>
       </c>
@@ -26706,7 +26706,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="174" spans="1:44" ht="14">
+    <row r="174" spans="1:44" ht="13.8">
       <c r="A174" s="5" t="s">
         <v>171</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="175" spans="1:44" ht="14" hidden="1">
+    <row r="175" spans="1:44" ht="13.8">
       <c r="A175" s="5" t="s">
         <v>138</v>
       </c>
@@ -26974,7 +26974,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="176" spans="1:44" ht="14">
+    <row r="176" spans="1:44" ht="13.8">
       <c r="A176" s="5" t="s">
         <v>139</v>
       </c>
@@ -27108,7 +27108,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="177" spans="1:44" ht="14" hidden="1">
+    <row r="177" spans="1:44" ht="13.8">
       <c r="A177" s="5" t="s">
         <v>140</v>
       </c>
@@ -27242,7 +27242,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="178" spans="1:44" ht="14" hidden="1">
+    <row r="178" spans="1:44" ht="13.8">
       <c r="A178" s="5" t="s">
         <v>145</v>
       </c>
@@ -27376,7 +27376,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="179" spans="1:44" ht="14" hidden="1">
+    <row r="179" spans="1:44" ht="13.8">
       <c r="A179" s="5" t="s">
         <v>141</v>
       </c>
@@ -27510,7 +27510,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="180" spans="1:44" ht="14">
+    <row r="180" spans="1:44" ht="13.8">
       <c r="A180" s="5" t="s">
         <v>142</v>
       </c>
@@ -27644,7 +27644,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="181" spans="1:44" ht="14">
+    <row r="181" spans="1:44" ht="13.8">
       <c r="A181" s="5" t="s">
         <v>172</v>
       </c>
@@ -27851,18 +27851,23 @@
       <c r="A205" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR181" xr:uid="{B0BB3401-F945-46E8-B4F3-7B13F6D043E4}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="CELLULAR.COM"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AR181" xr:uid="{B0BB3401-F945-46E8-B4F3-7B13F6D043E4}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c6f542b7-6ae1-4a12-b612-56d70bc1c7e1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f95a612f-f44e-4057-9b63-33d528109c08">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A48C4762DF4E454786F970AB8A28ECFB" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="51db5dd82d0243d9630b7cfa2f38ead8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95a612f-f44e-4057-9b63-33d528109c08" xmlns:ns3="c6f542b7-6ae1-4a12-b612-56d70bc1c7e1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="885defef1b4d2580f80fd221ae022ffd" ns2:_="" ns3:_="">
     <xsd:import namespace="f95a612f-f44e-4057-9b63-33d528109c08"/>
@@ -28063,7 +28068,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -28072,18 +28077,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c6f542b7-6ae1-4a12-b612-56d70bc1c7e1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f95a612f-f44e-4057-9b63-33d528109c08">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3927FAD3-E5A1-44F4-82D0-FFB5DAC8BD1A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c6f542b7-6ae1-4a12-b612-56d70bc1c7e1"/>
+    <ds:schemaRef ds:uri="f95a612f-f44e-4057-9b63-33d528109c08"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9612A2CB-9F5A-4186-89FC-F235820A9519}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28102,21 +28107,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2D8C6A8-03F1-4F8B-A9BC-760C91962565}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3927FAD3-E5A1-44F4-82D0-FFB5DAC8BD1A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c6f542b7-6ae1-4a12-b612-56d70bc1c7e1"/>
-    <ds:schemaRef ds:uri="f95a612f-f44e-4057-9b63-33d528109c08"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>